--- a/testdata/data.xlsx
+++ b/testdata/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Course\Playwright_typescript\playwrightJune26\CucumberFrameworkJune26\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA72500B-6D7D-40C8-8C72-DD553054F990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0D6DB7-07DD-404E-8068-6B5E9129DEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>Valid_login_TC01</t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>scenarioName</t>
+  </si>
+  <si>
+    <t>InValid_login_TC03_data_driven</t>
+  </si>
+  <si>
+    <t>lead_creation_TC04</t>
   </si>
 </sst>
 </file>
@@ -415,7 +421,7 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.9296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.46484375" bestFit="1" customWidth="1"/>
   </cols>
@@ -485,7 +491,9 @@
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -493,7 +501,9 @@
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>

--- a/testdata/data.xlsx
+++ b/testdata/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Course\Playwright_typescript\playwrightJune26\CucumberFrameworkJune26\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0D6DB7-07DD-404E-8068-6B5E9129DEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2922B4-F3B3-4CE4-A398-6351A17BF897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>Valid_login_TC01</t>
   </si>
@@ -70,6 +70,15 @@
   </si>
   <si>
     <t>lead_creation_TC04</t>
+  </si>
+  <si>
+    <t>List all your collection info</t>
+  </si>
+  <si>
+    <t>List all objects in a collection</t>
+  </si>
+  <si>
+    <t>Add a new object to a collection</t>
   </si>
 </sst>
 </file>
@@ -134,10 +143,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,7 +523,9 @@
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -519,7 +533,9 @@
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -527,7 +543,9 @@
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="2"/>
+      <c r="A9" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>

--- a/testdata/data.xlsx
+++ b/testdata/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Course\Playwright_typescript\playwrightJune26\CucumberFrameworkJune26\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2922B4-F3B3-4CE4-A398-6351A17BF897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4288DB-A90B-4FBD-A9CC-FEEF9CFE93B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>Valid_login_TC01</t>
   </si>
@@ -79,6 +79,15 @@
   </si>
   <si>
     <t>Add a new object to a collection</t>
+  </si>
+  <si>
+    <t>Update an object in a collection</t>
+  </si>
+  <si>
+    <t>Partially update an object in a collection</t>
+  </si>
+  <si>
+    <t>Delete an object from a collection</t>
   </si>
 </sst>
 </file>
@@ -116,7 +125,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -139,17 +148,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26.9296875" bestFit="1" customWidth="1"/>
@@ -552,6 +573,21 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
